--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397623</v>
+        <v>121397630</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624671</v>
+        <v>624663</v>
       </c>
       <c r="R2" t="n">
-        <v>6568664</v>
+        <v>6568653</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397630</v>
+        <v>121397623</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624663</v>
+        <v>624671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568653</v>
+        <v>6568664</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397626</v>
+        <v>121397623</v>
       </c>
       <c r="B3" t="n">
         <v>57720</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624593</v>
+        <v>624671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568665</v>
+        <v>6568664</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397623</v>
+        <v>121397626</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624671</v>
+        <v>624593</v>
       </c>
       <c r="R4" t="n">
-        <v>6568664</v>
+        <v>6568665</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397623</v>
+        <v>121397626</v>
       </c>
       <c r="B3" t="n">
         <v>57720</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624671</v>
+        <v>624593</v>
       </c>
       <c r="R3" t="n">
-        <v>6568664</v>
+        <v>6568665</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397626</v>
+        <v>121397623</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624593</v>
+        <v>624671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568665</v>
+        <v>6568664</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397630</v>
+        <v>121397623</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624663</v>
+        <v>624671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568653</v>
+        <v>6568664</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397623</v>
+        <v>121397630</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624671</v>
+        <v>624663</v>
       </c>
       <c r="R4" t="n">
-        <v>6568664</v>
+        <v>6568653</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397623</v>
+        <v>121397626</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624671</v>
+        <v>624593</v>
       </c>
       <c r="R2" t="n">
-        <v>6568664</v>
+        <v>6568665</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397626</v>
+        <v>121397623</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624593</v>
+        <v>624671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568665</v>
+        <v>6568664</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121397630</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397626</v>
+        <v>121397623</v>
       </c>
       <c r="B2" t="n">
         <v>57723</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624593</v>
+        <v>624671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568665</v>
+        <v>6568664</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397623</v>
+        <v>121397630</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624671</v>
+        <v>624663</v>
       </c>
       <c r="R3" t="n">
-        <v>6568664</v>
+        <v>6568653</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397630</v>
+        <v>121397626</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624663</v>
+        <v>624593</v>
       </c>
       <c r="R4" t="n">
-        <v>6568653</v>
+        <v>6568665</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121397623</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397630</v>
+        <v>121397626</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57724</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624663</v>
+        <v>624593</v>
       </c>
       <c r="R3" t="n">
-        <v>6568653</v>
+        <v>6568665</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397626</v>
+        <v>121397630</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624593</v>
+        <v>624663</v>
       </c>
       <c r="R4" t="n">
-        <v>6568665</v>
+        <v>6568653</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397623</v>
+        <v>121397630</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624671</v>
+        <v>624663</v>
       </c>
       <c r="R2" t="n">
-        <v>6568664</v>
+        <v>6568653</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -788,7 +788,7 @@
         <v>121397626</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397630</v>
+        <v>121397623</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624663</v>
+        <v>624671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568653</v>
+        <v>6568664</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397630</v>
+        <v>121397623</v>
       </c>
       <c r="B2" t="n">
-        <v>57375</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624663</v>
+        <v>624671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568653</v>
+        <v>6568664</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397626</v>
+        <v>121397630</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624593</v>
+        <v>624663</v>
       </c>
       <c r="R3" t="n">
-        <v>6568665</v>
+        <v>6568653</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397623</v>
+        <v>121397626</v>
       </c>
       <c r="B4" t="n">
         <v>57725</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624671</v>
+        <v>624593</v>
       </c>
       <c r="R4" t="n">
-        <v>6568664</v>
+        <v>6568665</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397623</v>
+        <v>121397626</v>
       </c>
       <c r="B2" t="n">
         <v>57725</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624671</v>
+        <v>624593</v>
       </c>
       <c r="R2" t="n">
-        <v>6568664</v>
+        <v>6568665</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397626</v>
+        <v>121397623</v>
       </c>
       <c r="B4" t="n">
         <v>57725</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624593</v>
+        <v>624671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568665</v>
+        <v>6568664</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397630</v>
+        <v>121397623</v>
       </c>
       <c r="B3" t="n">
-        <v>57375</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624663</v>
+        <v>624671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568653</v>
+        <v>6568664</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397623</v>
+        <v>121397630</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624671</v>
+        <v>624663</v>
       </c>
       <c r="R4" t="n">
-        <v>6568664</v>
+        <v>6568653</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>

--- a/artfynd/A 19598-2024 artfynd.xlsx
+++ b/artfynd/A 19598-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121397626</v>
+        <v>121397623</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624593</v>
+        <v>624671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568665</v>
+        <v>6568664</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121397623</v>
+        <v>121397630</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624671</v>
+        <v>624663</v>
       </c>
       <c r="R3" t="n">
-        <v>6568664</v>
+        <v>6568653</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121397630</v>
+        <v>121397626</v>
       </c>
       <c r="B4" t="n">
-        <v>57375</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624663</v>
+        <v>624593</v>
       </c>
       <c r="R4" t="n">
-        <v>6568653</v>
+        <v>6568665</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
